--- a/survey_templates/024_judgment_and_repentance_survey--survey_templates.xlsx
+++ b/survey_templates/024_judgment_and_repentance_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>How did you feel after committing the behavior?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>remorse</t>
+          <t>remorse_nature</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>remorse</t>
+          <t>What was the nature of your remorse after the behavior?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>forgiveness</t>
+          <t>remorse_response</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>forgiveness</t>
+          <t>How did you respond to your remorse?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>repentance</t>
+          <t>remorse_frequency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>repentance</t>
+          <t>How often do you experience feelings of remorse after your actions?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>attitude</t>
+          <t>remorse_strength</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>attitude</t>
+          <t>How strongly do you associate remorse with personal change?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>remorse_scale</t>
+          <t>self_reflection_attitude</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>remorse_scale</t>
+          <t>What is your attitude towards self-reflection and introspection?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,41 +681,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>remorse_scale_description</t>
+          <t>remorse_guilt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>remorse_scale_description</t>
+          <t>What is the relationship between remorse and personal growth?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>repentance_scale</t>
+          <t>remorse_in_others</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>repentance_scale</t>
+          <t>How do you respond to feelings of remorse in others?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>remorse_scale_description</t>
+          <t>guilt_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>remorse_scale_description</t>
+          <t>How often do you experience feelings of guilt after your actions?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>remorse_scale_value</t>
+          <t>remorse_intensity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>remorse_scale_value</t>
+          <t>What is the value of remorse in personal and social relationships?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>repentance_scale_value</t>
+          <t>remorse_measurement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>repentance_scale_value</t>
+          <t>How do you measure the intensity of remorse?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,58 +796,58 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>remorse_frequency</t>
+          <t>repentance_frequency</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>remorse_frequency</t>
+          <t>How frequently do you repent for past actions?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>remorse_frequency_description</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>remorse_frequency_description</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>remorse_intensity</t>
+          <t>submission</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>remorse_intensity</t>
+          <t>Submission Date</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>remorse_intensity_description</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>remorse_intensity_description</t>
+          <t>Submission Time</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,294 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>repentance_frequency</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>repentance_frequency</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>repentance_frequency_description</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>repentance_frequency_description</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>remorse_intensity</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>remorse_intensity</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>remorse_intensity_description</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>remorse_intensity_description</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>repentance_intensity</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>repentance_intensity</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>remorse_value</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>remorse_value</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>remorse_value_description</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>remorse_value_description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>repentance_value</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>repentance_value</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>repentance_value_description</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>repentance_value_description</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1193,7 +917,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1218,7 +942,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>forgiveness_choices</t>
+          <t>remorse_response_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1228,14 +952,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>forgiveness_choices</t>
+          <t>remorse_response_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1245,14 +969,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>repentance_choices</t>
+          <t>remorse_in_others_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1262,14 +986,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>repentance_choices</t>
+          <t>remorse_in_others_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1279,7 +1003,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>No</t>
         </is>
       </c>
     </row>
